--- a/xlsx/data.xlsx
+++ b/xlsx/data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\Project\whats-your-color\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\Project\whats-your-color\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9087244E-CDD7-4776-AC4A-5C53D5C9DEBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26A5AD22-5D55-469C-B088-A9F61D5D44C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4338" uniqueCount="2786">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4337" uniqueCount="2786">
   <si>
     <t>เลข</t>
   </si>
@@ -8384,7 +8384,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -8413,6 +8413,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="13">
@@ -8516,7 +8522,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -8554,6 +8560,7 @@
     <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8856,7 +8863,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F723"/>
+  <dimension ref="A1:F724"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -23311,8 +23318,8 @@
       <c r="A723" s="2" t="s">
         <v>2785</v>
       </c>
-      <c r="B723" s="2" t="s">
-        <v>2133</v>
+      <c r="B723" s="2">
+        <v>6913287016</v>
       </c>
       <c r="C723" s="2" t="s">
         <v>38</v>
@@ -23326,6 +23333,9 @@
       <c r="F723" s="12" t="s">
         <v>1945</v>
       </c>
+    </row>
+    <row r="724" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+      <c r="B724" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
